--- a/Excel Practice @ Day 03 New.xlsx
+++ b/Excel Practice @ Day 03 New.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Codegnan\Data Analytics\Microsoft Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ccb28e096d3d1180/Desktop/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7B37C2-DB3D-432E-A6F9-1913D8281B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient_Data" sheetId="1" r:id="rId1"/>
@@ -1404,26 +1404,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T66"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.109375" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="6" max="6" width="15.90625" customWidth="1"/>
+    <col min="7" max="7" width="18.36328125" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" customWidth="1"/>
-    <col min="11" max="11" width="16.88671875" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="14.77734375" customWidth="1"/>
-    <col min="16" max="16" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" customWidth="1"/>
+    <col min="10" max="10" width="19.54296875" customWidth="1"/>
+    <col min="11" max="11" width="16.90625" customWidth="1"/>
+    <col min="12" max="12" width="18.453125" customWidth="1"/>
+    <col min="13" max="13" width="16.453125" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="15" max="15" width="14.81640625" customWidth="1"/>
+    <col min="16" max="16" width="15.90625" customWidth="1"/>
     <col min="17" max="17" width="21" customWidth="1"/>
-    <col min="18" max="18" width="17.33203125" customWidth="1"/>
-    <col min="19" max="19" width="17.6640625" customWidth="1"/>
-    <col min="20" max="20" width="18.109375" customWidth="1"/>
+    <col min="18" max="18" width="17.36328125" customWidth="1"/>
+    <col min="19" max="19" width="17.6328125" customWidth="1"/>
+    <col min="20" max="20" width="18.08984375" customWidth="1"/>
     <col min="22" max="22" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3301,9 +3301,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0CC642-27D6-44E5-9163-DA270655D0F5}">
   <dimension ref="A1:C47"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="98.109375" customWidth="1"/>
+    <col min="1" max="1" width="98.08984375" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3516,11 +3516,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC1AF7B-FEF6-4828-8271-552716DAF040}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3915,7 +3915,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="28.8">
+    <row r="29" spans="1:4" ht="29">
       <c r="A29" s="3">
         <v>16</v>
       </c>
